--- a/2号文档完整填充模板2.0.xlsx
+++ b/2号文档完整填充模板2.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\idealcprofessional\projects\DocAutoGenByExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490849B0-0FE1-4D89-8F66-866FA694CAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CC1DD8-1FEA-489B-8BBA-2E47535ACE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="113">
   <si>
     <t>模块编号</t>
   </si>
@@ -462,6 +462,14 @@
   </si>
   <si>
     <t>测试结论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.6.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.2026.6.256.25</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -469,7 +477,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,6 +530,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -543,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -579,6 +596,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -949,7 +967,9 @@
         <v>8</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="E2" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
@@ -980,7 +1000,9 @@
         <v>8</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1019,7 +1041,9 @@
         <v>8</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F4" s="5" t="s">
         <v>9</v>
       </c>
@@ -1058,7 +1082,9 @@
         <v>8</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F5" s="5" t="s">
         <v>9</v>
       </c>
@@ -1080,7 +1106,9 @@
         <v>8</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F6" s="5" t="s">
         <v>9</v>
       </c>
@@ -1111,7 +1139,9 @@
         <v>8</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F7" s="5" t="s">
         <v>9</v>
       </c>
@@ -1142,7 +1172,9 @@
         <v>8</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F8" s="5" t="s">
         <v>9</v>
       </c>
@@ -1164,7 +1196,9 @@
         <v>8</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F9" s="5" t="s">
         <v>9</v>
       </c>
@@ -1186,7 +1220,9 @@
         <v>8</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F10" s="5" t="s">
         <v>9</v>
       </c>
@@ -1208,7 +1244,9 @@
         <v>8</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F11" s="5" t="s">
         <v>9</v>
       </c>
@@ -1252,7 +1290,9 @@
         <v>8</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F13" s="5" t="s">
         <v>9</v>
       </c>
@@ -1274,6 +1314,9 @@
         <v>8</v>
       </c>
       <c r="D14" s="2"/>
+      <c r="E14" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F14" s="9" t="s">
         <v>44</v>
       </c>
@@ -1299,6 +1342,9 @@
         <v>8</v>
       </c>
       <c r="D15" s="2"/>
+      <c r="E15" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F15" s="9" t="s">
         <v>46</v>
       </c>
@@ -1324,6 +1370,9 @@
         <v>8</v>
       </c>
       <c r="D16" s="2"/>
+      <c r="E16" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F16" s="9" t="s">
         <v>48</v>
       </c>
@@ -1349,6 +1398,9 @@
         <v>8</v>
       </c>
       <c r="D17" s="2"/>
+      <c r="E17" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F17" s="9" t="s">
         <v>50</v>
       </c>
@@ -1374,6 +1426,9 @@
         <v>8</v>
       </c>
       <c r="D18" s="2"/>
+      <c r="E18" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F18" s="9" t="s">
         <v>52</v>
       </c>
@@ -1399,6 +1454,9 @@
         <v>8</v>
       </c>
       <c r="D19" s="2"/>
+      <c r="E19" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F19" s="9" t="s">
         <v>54</v>
       </c>
@@ -1424,6 +1482,9 @@
         <v>8</v>
       </c>
       <c r="D20" s="2"/>
+      <c r="E20" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F20" s="9" t="s">
         <v>56</v>
       </c>
@@ -1474,6 +1535,9 @@
         <v>8</v>
       </c>
       <c r="D22" s="2"/>
+      <c r="E22" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F22" s="9" t="s">
         <v>60</v>
       </c>
@@ -1499,6 +1563,9 @@
         <v>8</v>
       </c>
       <c r="D23" s="2"/>
+      <c r="E23" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F23" s="7" t="s">
         <v>62</v>
       </c>
@@ -1549,6 +1616,9 @@
         <v>8</v>
       </c>
       <c r="D25" s="2"/>
+      <c r="E25" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F25" s="7" t="s">
         <v>67</v>
       </c>
@@ -1574,6 +1644,9 @@
         <v>8</v>
       </c>
       <c r="D26" s="2"/>
+      <c r="E26" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F26" s="7" t="s">
         <v>69</v>
       </c>
@@ -1599,6 +1672,9 @@
         <v>8</v>
       </c>
       <c r="D27" s="2"/>
+      <c r="E27" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F27" s="7" t="s">
         <v>71</v>
       </c>
@@ -1649,6 +1725,9 @@
         <v>8</v>
       </c>
       <c r="D29" s="2"/>
+      <c r="E29" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="F29" s="7" t="s">
         <v>75</v>
       </c>
@@ -1699,6 +1778,9 @@
         <v>8</v>
       </c>
       <c r="D31" s="2"/>
+      <c r="E31" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F31" s="7" t="s">
         <v>80</v>
       </c>
@@ -1731,6 +1813,9 @@
         <v>82</v>
       </c>
       <c r="D33" s="10"/>
+      <c r="E33" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F33" s="11" t="s">
         <v>83</v>
       </c>
@@ -1756,6 +1841,9 @@
         <v>86</v>
       </c>
       <c r="D34" s="10"/>
+      <c r="E34" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F34" s="11" t="s">
         <v>87</v>
       </c>
@@ -1781,6 +1869,9 @@
         <v>90</v>
       </c>
       <c r="D35" s="10"/>
+      <c r="E35" s="13" t="s">
+        <v>111</v>
+      </c>
       <c r="F35" s="11" t="s">
         <v>91</v>
       </c>
@@ -1806,6 +1897,9 @@
         <v>94</v>
       </c>
       <c r="D36" s="10"/>
+      <c r="E36" s="13" t="s">
+        <v>111</v>
+      </c>
       <c r="F36" s="11" t="s">
         <v>95</v>
       </c>
@@ -1831,6 +1925,9 @@
         <v>98</v>
       </c>
       <c r="D37" s="10"/>
+      <c r="E37" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="F37" s="11" t="s">
         <v>99</v>
       </c>
